--- a/backend/data/financials_by_company/1002.HK.xlsx
+++ b/backend/data/financials_by_company/1002.HK.xlsx
@@ -682,203 +682,209 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45504</v>
+        <v>44408</v>
       </c>
       <c r="B2" t="n">
-        <v>6401835</v>
+        <v>-1699005</v>
       </c>
       <c r="C2" t="n">
         <v>0.165</v>
       </c>
       <c r="D2" t="n">
-        <v>-45442000</v>
+        <v>35877000</v>
       </c>
       <c r="E2" t="n">
-        <v>38799000</v>
+        <v>-10297000</v>
       </c>
       <c r="F2" t="n">
-        <v>38799000</v>
+        <v>-10297000</v>
       </c>
       <c r="G2" t="n">
-        <v>-9502000</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>-5612000</v>
+      </c>
+      <c r="H2" t="n">
+        <v>24691000</v>
+      </c>
       <c r="I2" t="n">
-        <v>49234000</v>
+        <v>201889000</v>
       </c>
       <c r="J2" t="n">
-        <v>-6643000</v>
+        <v>25580000</v>
       </c>
       <c r="K2" t="n">
-        <v>-6643000</v>
+        <v>889000</v>
       </c>
       <c r="L2" t="n">
-        <v>-349000</v>
+        <v>-5705000</v>
       </c>
       <c r="M2" t="n">
-        <v>1687000</v>
+        <v>6080000</v>
       </c>
       <c r="N2" t="n">
-        <v>1476000</v>
+        <v>518000</v>
       </c>
       <c r="O2" t="n">
-        <v>-41899165</v>
+        <v>2985995</v>
       </c>
       <c r="P2" t="n">
-        <v>-9502000</v>
+        <v>-5612000</v>
       </c>
       <c r="Q2" t="n">
-        <v>107907000</v>
+        <v>247842000</v>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>-21254000</v>
-      </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+        <v>-3933000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2307513000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2307513000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-0.0024</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-0.0024</v>
+      </c>
       <c r="X2" t="n">
-        <v>-9502000</v>
+        <v>-5612000</v>
       </c>
       <c r="Y2" t="n">
-        <v>-9502000</v>
+        <v>-5612000</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-9502000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-699000</v>
-      </c>
+        <v>-5612000</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>-8803000</v>
+        <v>-5612000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-8803000</v>
+        <v>-5612000</v>
       </c>
       <c r="AE2" t="n">
-        <v>473000</v>
+        <v>421000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-8330000</v>
+        <v>-5191000</v>
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="n">
-        <v>38799000</v>
+        <v>-10297000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-908000</v>
+        <v>-3684000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-9223000</v>
+        <v>4810000</v>
       </c>
       <c r="AK2" t="n">
-        <v>21077000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-49745000</v>
-      </c>
+        <v>9171000</v>
+      </c>
+      <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="n">
-        <v>-349000</v>
+        <v>-5705000</v>
       </c>
       <c r="AN2" t="n">
-        <v>138000</v>
+        <v>143000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1687000</v>
+        <v>6080000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1476000</v>
+        <v>518000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-51863000</v>
+        <v>8354000</v>
       </c>
       <c r="AR2" t="n">
-        <v>58673000</v>
+        <v>45953000</v>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
-        <v>63644000</v>
+        <v>50975000</v>
       </c>
       <c r="AU2" t="n">
-        <v>1290000</v>
+        <v>5901000</v>
       </c>
       <c r="AV2" t="n">
-        <v>62354000</v>
+        <v>45074000</v>
       </c>
       <c r="AW2" t="n">
-        <v>6810000</v>
+        <v>54307000</v>
       </c>
       <c r="AX2" t="n">
-        <v>49234000</v>
+        <v>201889000</v>
       </c>
       <c r="AY2" t="n">
-        <v>56044000</v>
+        <v>256196000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>56044000</v>
+        <v>256196000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45138</v>
+        <v>44773</v>
       </c>
       <c r="B3" t="n">
-        <v>-1571130</v>
+        <v>-41075.370539</v>
       </c>
       <c r="C3" t="n">
-        <v>0.165</v>
+        <v>0.001263</v>
       </c>
       <c r="D3" t="n">
-        <v>2452000</v>
+        <v>9114000</v>
       </c>
       <c r="E3" t="n">
-        <v>-9522000</v>
+        <v>-32529000</v>
       </c>
       <c r="F3" t="n">
-        <v>-9522000</v>
+        <v>-32529000</v>
       </c>
       <c r="G3" t="n">
-        <v>-22320000</v>
+        <v>-48247000</v>
       </c>
       <c r="H3" t="n">
-        <v>13458000</v>
+        <v>22781000</v>
       </c>
       <c r="I3" t="n">
-        <v>64932000</v>
+        <v>111227000</v>
       </c>
       <c r="J3" t="n">
-        <v>-7070000</v>
+        <v>-23415000</v>
       </c>
       <c r="K3" t="n">
-        <v>-20528000</v>
+        <v>-46196000</v>
       </c>
       <c r="L3" t="n">
-        <v>-910000</v>
+        <v>-1162000</v>
       </c>
       <c r="M3" t="n">
-        <v>1764000</v>
+        <v>2112000</v>
       </c>
       <c r="N3" t="n">
-        <v>921000</v>
+        <v>1056000</v>
       </c>
       <c r="O3" t="n">
-        <v>-14369130</v>
+        <v>-15759075.370539</v>
       </c>
       <c r="P3" t="n">
-        <v>-22320000</v>
+        <v>-48247000</v>
       </c>
       <c r="Q3" t="n">
-        <v>90863000</v>
+        <v>144567000</v>
       </c>
       <c r="R3" t="n">
-        <v>1495000</v>
+        <v>1492000</v>
       </c>
       <c r="S3" t="n">
-        <v>-23784000</v>
+        <v>-49276000</v>
       </c>
       <c r="T3" t="n">
         <v>2307513000</v>
@@ -887,152 +893,152 @@
         <v>2307513000</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.0097</v>
+        <v>-0.0209</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.0097</v>
+        <v>-0.0209</v>
       </c>
       <c r="X3" t="n">
-        <v>-22320000</v>
+        <v>-48247000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-22320000</v>
+        <v>-48247000</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-22320000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
+        <v>-48247000</v>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>-22320000</v>
+        <v>-48247000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-22320000</v>
+        <v>-48247000</v>
       </c>
       <c r="AE3" t="n">
-        <v>28000</v>
+        <v>-61000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-22292000</v>
-      </c>
-      <c r="AG3" t="inlineStr"/>
+        <v>-48308000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>5013000</v>
+      </c>
       <c r="AH3" t="n">
-        <v>-9522000</v>
+        <v>-32529000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-2001000</v>
+        <v>4807000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>27000</v>
+        <v>12000</v>
       </c>
       <c r="AK3" t="n">
-        <v>11496000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
+        <v>27710000</v>
+      </c>
+      <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="n">
-        <v>-910000</v>
+        <v>-1162000</v>
       </c>
       <c r="AN3" t="n">
-        <v>67000</v>
+        <v>106000</v>
       </c>
       <c r="AO3" t="n">
-        <v>1764000</v>
+        <v>2112000</v>
       </c>
       <c r="AP3" t="n">
-        <v>921000</v>
+        <v>1056000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-14420000</v>
+        <v>-23166000</v>
       </c>
       <c r="AR3" t="n">
-        <v>25931000</v>
-      </c>
-      <c r="AS3" t="inlineStr"/>
+        <v>33340000</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>-5013000</v>
+      </c>
       <c r="AT3" t="n">
-        <v>30448000</v>
+        <v>37903000</v>
       </c>
       <c r="AU3" t="n">
-        <v>1659000</v>
+        <v>3209000</v>
       </c>
       <c r="AV3" t="n">
-        <v>28789000</v>
+        <v>34694000</v>
       </c>
       <c r="AW3" t="n">
-        <v>11511000</v>
+        <v>10174000</v>
       </c>
       <c r="AX3" t="n">
-        <v>64932000</v>
+        <v>111227000</v>
       </c>
       <c r="AY3" t="n">
-        <v>76443000</v>
+        <v>121401000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>76443000</v>
+        <v>121401000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44773</v>
+        <v>45138</v>
       </c>
       <c r="B4" t="n">
-        <v>-41075.370539</v>
+        <v>-1571130</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001263</v>
+        <v>0.165</v>
       </c>
       <c r="D4" t="n">
-        <v>9114000</v>
+        <v>2452000</v>
       </c>
       <c r="E4" t="n">
-        <v>-32529000</v>
+        <v>-9522000</v>
       </c>
       <c r="F4" t="n">
-        <v>-32529000</v>
+        <v>-9522000</v>
       </c>
       <c r="G4" t="n">
-        <v>-48247000</v>
+        <v>-22320000</v>
       </c>
       <c r="H4" t="n">
-        <v>22781000</v>
+        <v>13458000</v>
       </c>
       <c r="I4" t="n">
-        <v>111227000</v>
+        <v>64932000</v>
       </c>
       <c r="J4" t="n">
-        <v>-23415000</v>
+        <v>-7070000</v>
       </c>
       <c r="K4" t="n">
-        <v>-46196000</v>
+        <v>-20528000</v>
       </c>
       <c r="L4" t="n">
-        <v>-1162000</v>
+        <v>-910000</v>
       </c>
       <c r="M4" t="n">
-        <v>2112000</v>
+        <v>1764000</v>
       </c>
       <c r="N4" t="n">
-        <v>1056000</v>
+        <v>921000</v>
       </c>
       <c r="O4" t="n">
-        <v>-15759075.370539</v>
+        <v>-14369130</v>
       </c>
       <c r="P4" t="n">
-        <v>-48247000</v>
+        <v>-22320000</v>
       </c>
       <c r="Q4" t="n">
-        <v>144567000</v>
+        <v>90863000</v>
       </c>
       <c r="R4" t="n">
-        <v>1492000</v>
+        <v>1495000</v>
       </c>
       <c r="S4" t="n">
-        <v>-49276000</v>
+        <v>-23784000</v>
       </c>
       <c r="T4" t="n">
         <v>2307513000</v>
@@ -1041,241 +1047,235 @@
         <v>2307513000</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.0209</v>
+        <v>-0.0097</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.0209</v>
+        <v>-0.0097</v>
       </c>
       <c r="X4" t="n">
-        <v>-48247000</v>
+        <v>-22320000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-48247000</v>
+        <v>-22320000</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-48247000</v>
-      </c>
-      <c r="AB4" t="inlineStr"/>
+        <v>-22320000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
       <c r="AC4" t="n">
-        <v>-48247000</v>
+        <v>-22320000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-48247000</v>
+        <v>-22320000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-61000</v>
+        <v>28000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-48308000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>5013000</v>
-      </c>
+        <v>-22292000</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>-32529000</v>
+        <v>-9522000</v>
       </c>
       <c r="AI4" t="n">
-        <v>4807000</v>
+        <v>-2001000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>12000</v>
+        <v>27000</v>
       </c>
       <c r="AK4" t="n">
-        <v>27710000</v>
-      </c>
-      <c r="AL4" t="inlineStr"/>
+        <v>11496000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
       <c r="AM4" t="n">
-        <v>-1162000</v>
+        <v>-910000</v>
       </c>
       <c r="AN4" t="n">
-        <v>106000</v>
+        <v>67000</v>
       </c>
       <c r="AO4" t="n">
-        <v>2112000</v>
+        <v>1764000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1056000</v>
+        <v>921000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-23166000</v>
+        <v>-14420000</v>
       </c>
       <c r="AR4" t="n">
-        <v>33340000</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>-5013000</v>
-      </c>
+        <v>25931000</v>
+      </c>
+      <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>37903000</v>
+        <v>30448000</v>
       </c>
       <c r="AU4" t="n">
-        <v>3209000</v>
+        <v>1659000</v>
       </c>
       <c r="AV4" t="n">
-        <v>34694000</v>
+        <v>28789000</v>
       </c>
       <c r="AW4" t="n">
-        <v>10174000</v>
+        <v>11511000</v>
       </c>
       <c r="AX4" t="n">
-        <v>111227000</v>
+        <v>64932000</v>
       </c>
       <c r="AY4" t="n">
-        <v>121401000</v>
+        <v>76443000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>121401000</v>
+        <v>76443000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44408</v>
+        <v>45504</v>
       </c>
       <c r="B5" t="n">
-        <v>-1699005</v>
+        <v>6401835</v>
       </c>
       <c r="C5" t="n">
         <v>0.165</v>
       </c>
       <c r="D5" t="n">
-        <v>35877000</v>
+        <v>-45442000</v>
       </c>
       <c r="E5" t="n">
-        <v>-10297000</v>
+        <v>38799000</v>
       </c>
       <c r="F5" t="n">
-        <v>-10297000</v>
+        <v>38799000</v>
       </c>
       <c r="G5" t="n">
-        <v>-5612000</v>
-      </c>
-      <c r="H5" t="n">
-        <v>24691000</v>
-      </c>
+        <v>-9502000</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>201889000</v>
+        <v>49234000</v>
       </c>
       <c r="J5" t="n">
-        <v>25580000</v>
+        <v>-6643000</v>
       </c>
       <c r="K5" t="n">
-        <v>889000</v>
+        <v>-6643000</v>
       </c>
       <c r="L5" t="n">
-        <v>-5705000</v>
+        <v>-349000</v>
       </c>
       <c r="M5" t="n">
-        <v>6080000</v>
+        <v>1687000</v>
       </c>
       <c r="N5" t="n">
-        <v>518000</v>
+        <v>1476000</v>
       </c>
       <c r="O5" t="n">
-        <v>2985995</v>
+        <v>-41899165</v>
       </c>
       <c r="P5" t="n">
-        <v>-5612000</v>
+        <v>-9502000</v>
       </c>
       <c r="Q5" t="n">
-        <v>247842000</v>
+        <v>107907000</v>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>-3933000</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2307513000</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2307513000</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-0.0024</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-0.0024</v>
-      </c>
+        <v>-21254000</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>-5612000</v>
+        <v>-9502000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-5612000</v>
+        <v>-9502000</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-5612000</v>
-      </c>
-      <c r="AB5" t="inlineStr"/>
+        <v>-9502000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-699000</v>
+      </c>
       <c r="AC5" t="n">
-        <v>-5612000</v>
+        <v>-8803000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-5612000</v>
+        <v>-8803000</v>
       </c>
       <c r="AE5" t="n">
-        <v>421000</v>
+        <v>473000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-5191000</v>
+        <v>-8330000</v>
       </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>-10297000</v>
+        <v>38799000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-3684000</v>
+        <v>-908000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4810000</v>
+        <v>-9223000</v>
       </c>
       <c r="AK5" t="n">
-        <v>9171000</v>
-      </c>
-      <c r="AL5" t="inlineStr"/>
+        <v>21077000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-49745000</v>
+      </c>
       <c r="AM5" t="n">
-        <v>-5705000</v>
+        <v>-349000</v>
       </c>
       <c r="AN5" t="n">
-        <v>143000</v>
+        <v>138000</v>
       </c>
       <c r="AO5" t="n">
-        <v>6080000</v>
+        <v>1687000</v>
       </c>
       <c r="AP5" t="n">
-        <v>518000</v>
+        <v>1476000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8354000</v>
+        <v>-51863000</v>
       </c>
       <c r="AR5" t="n">
-        <v>45953000</v>
+        <v>58673000</v>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>50975000</v>
+        <v>63644000</v>
       </c>
       <c r="AU5" t="n">
-        <v>5901000</v>
+        <v>1290000</v>
       </c>
       <c r="AV5" t="n">
-        <v>45074000</v>
+        <v>62354000</v>
       </c>
       <c r="AW5" t="n">
-        <v>54307000</v>
+        <v>6810000</v>
       </c>
       <c r="AX5" t="n">
-        <v>201889000</v>
+        <v>49234000</v>
       </c>
       <c r="AY5" t="n">
-        <v>256196000</v>
+        <v>56044000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>256196000</v>
+        <v>56044000</v>
       </c>
     </row>
   </sheetData>
@@ -1626,200 +1626,202 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45504</v>
+        <v>44408</v>
       </c>
       <c r="B2" t="n">
-        <v>2511084792</v>
+        <v>2307513000</v>
       </c>
       <c r="C2" t="n">
-        <v>2511084792</v>
+        <v>2307513000</v>
       </c>
       <c r="D2" t="n">
-        <v>43550000</v>
+        <v>46434000</v>
       </c>
       <c r="E2" t="n">
-        <v>147813000</v>
+        <v>89845000</v>
       </c>
       <c r="F2" t="n">
-        <v>266034000</v>
+        <v>338260000</v>
       </c>
       <c r="G2" t="n">
-        <v>410572000</v>
+        <v>440432000</v>
       </c>
       <c r="H2" t="n">
-        <v>41678000</v>
+        <v>91933000</v>
       </c>
       <c r="I2" t="n">
-        <v>266034000</v>
+        <v>338260000</v>
       </c>
       <c r="J2" t="n">
-        <v>19613000</v>
+        <v>215000</v>
       </c>
       <c r="K2" t="n">
-        <v>282372000</v>
+        <v>350802000</v>
       </c>
       <c r="L2" t="n">
-        <v>308833000</v>
+        <v>386807000</v>
       </c>
       <c r="M2" t="n">
-        <v>342752000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>60380000</v>
-      </c>
+        <v>350802000</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>282372000</v>
+        <v>350802000</v>
       </c>
       <c r="P2" t="n">
-        <v>-215773000</v>
+        <v>-60575000</v>
       </c>
       <c r="Q2" t="n">
-        <v>310099000</v>
+        <v>306364000</v>
       </c>
       <c r="R2" t="n">
-        <v>114351000</v>
+        <v>105013000</v>
       </c>
       <c r="S2" t="n">
-        <v>114351000</v>
+        <v>105013000</v>
       </c>
       <c r="T2" t="n">
-        <v>250991000</v>
+        <v>141154000</v>
       </c>
       <c r="U2" t="n">
-        <v>48138000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>2802000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>864000</v>
-      </c>
+        <v>38828000</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
-        <v>4881000</v>
+        <v>2823000</v>
       </c>
       <c r="Y2" t="n">
-        <v>39591000</v>
+        <v>36005000</v>
       </c>
       <c r="Z2" t="n">
-        <v>13130000</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>26461000</v>
+        <v>36005000</v>
       </c>
       <c r="AB2" t="n">
-        <v>202853000</v>
+        <v>102326000</v>
       </c>
       <c r="AC2" t="n">
-        <v>108222000</v>
+        <v>53840000</v>
       </c>
       <c r="AD2" t="n">
-        <v>6483000</v>
+        <v>215000</v>
       </c>
       <c r="AE2" t="n">
-        <v>101739000</v>
+        <v>53625000</v>
       </c>
       <c r="AF2" t="n">
-        <v>61472000</v>
+        <v>23559000</v>
       </c>
       <c r="AG2" t="n">
-        <v>3548000</v>
+        <v>796000</v>
       </c>
       <c r="AH2" t="n">
-        <v>556000</v>
+        <v>61000</v>
       </c>
       <c r="AI2" t="n">
-        <v>57368000</v>
+        <v>22702000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>593743000</v>
+        <v>491956000</v>
       </c>
       <c r="AK2" t="n">
-        <v>349212000</v>
+        <v>297697000</v>
       </c>
       <c r="AL2" t="n">
-        <v>4486000</v>
+        <v>1027000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
+        <v>3700000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>3700000</v>
+      </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>5366000</v>
       </c>
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="n">
-        <v>16338000</v>
+        <v>12542000</v>
       </c>
       <c r="AR2" t="n">
-        <v>16338000</v>
+        <v>12542000</v>
       </c>
       <c r="AS2" t="n">
-        <v>326045000</v>
+        <v>275062000</v>
       </c>
       <c r="AT2" t="n">
-        <v>-652550000</v>
+        <v>-611636000</v>
       </c>
       <c r="AU2" t="n">
-        <v>978595000</v>
-      </c>
-      <c r="AV2" t="inlineStr"/>
+        <v>886698000</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
       <c r="AW2" t="n">
-        <v>947564000</v>
+        <v>287604000</v>
       </c>
       <c r="AX2" t="n">
-        <v>31031000</v>
-      </c>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
+        <v>608294000</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>278404000</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
       <c r="BA2" t="n">
-        <v>244531000</v>
+        <v>194259000</v>
       </c>
       <c r="BB2" t="n">
-        <v>13154000</v>
+        <v>48435000</v>
       </c>
       <c r="BC2" t="n">
-        <v>84971000</v>
+        <v>24435000</v>
       </c>
       <c r="BD2" t="n">
-        <v>-9447000</v>
+        <v>-8361000</v>
       </c>
       <c r="BE2" t="n">
-        <v>30754000</v>
+        <v>14208000</v>
       </c>
       <c r="BF2" t="n">
-        <v>10478000</v>
+        <v>1077000</v>
       </c>
       <c r="BG2" t="n">
-        <v>53186000</v>
+        <v>17511000</v>
       </c>
       <c r="BH2" t="n">
-        <v>6162000</v>
+        <v>38508000</v>
       </c>
       <c r="BI2" t="n">
-        <v>55594000</v>
+        <v>39685000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>-325000</v>
       </c>
       <c r="BK2" t="n">
-        <v>55594000</v>
+        <v>40010000</v>
       </c>
       <c r="BL2" t="n">
-        <v>84650000</v>
+        <v>43196000</v>
       </c>
       <c r="BM2" t="n">
-        <v>84650000</v>
+        <v>43196000</v>
       </c>
       <c r="BN2" t="n">
-        <v>170000</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>84480000</v>
+        <v>43196000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45138</v>
+        <v>44773</v>
       </c>
       <c r="B3" t="n">
         <v>2307513000</v>
@@ -1829,40 +1831,38 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>35108000</v>
+        <v>37413000</v>
       </c>
       <c r="F3" t="n">
-        <v>267566000</v>
+        <v>289816000</v>
       </c>
       <c r="G3" t="n">
-        <v>314410000</v>
+        <v>339368000</v>
       </c>
       <c r="H3" t="n">
-        <v>69203000</v>
+        <v>105086000</v>
       </c>
       <c r="I3" t="n">
-        <v>267566000</v>
+        <v>289816000</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>279302000</v>
+        <v>301955000</v>
       </c>
       <c r="L3" t="n">
-        <v>279302000</v>
+        <v>339368000</v>
       </c>
       <c r="M3" t="n">
-        <v>279302000</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
+        <v>301955000</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>279302000</v>
+        <v>301955000</v>
       </c>
       <c r="P3" t="n">
-        <v>-200373000</v>
+        <v>-178071000</v>
       </c>
       <c r="Q3" t="n">
         <v>306364000</v>
@@ -1874,149 +1874,145 @@
         <v>105013000</v>
       </c>
       <c r="T3" t="n">
-        <v>52405000</v>
+        <v>66581000</v>
       </c>
       <c r="U3" t="n">
-        <v>920000</v>
+        <v>38329000</v>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>920000</v>
+        <v>916000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
+        <v>37413000</v>
+      </c>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>37413000</v>
       </c>
       <c r="AB3" t="n">
-        <v>51485000</v>
+        <v>28252000</v>
       </c>
       <c r="AC3" t="n">
-        <v>35108000</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>35108000</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>8048000</v>
+        <v>8702000</v>
       </c>
       <c r="AG3" t="n">
-        <v>592000</v>
+        <v>733000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>93000</v>
       </c>
       <c r="AI3" t="n">
-        <v>7456000</v>
+        <v>7876000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>331707000</v>
+        <v>368536000</v>
       </c>
       <c r="AK3" t="n">
-        <v>211019000</v>
+        <v>235198000</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>2300000</v>
+        <v>3100000</v>
       </c>
       <c r="AN3" t="n">
-        <v>2300000</v>
+        <v>3100000</v>
       </c>
       <c r="AO3" t="n">
-        <v>10365000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
+        <v>7496000</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="n">
-        <v>11736000</v>
+        <v>12139000</v>
       </c>
       <c r="AR3" t="n">
-        <v>11736000</v>
+        <v>12139000</v>
       </c>
       <c r="AS3" t="n">
-        <v>186618000</v>
+        <v>212463000</v>
       </c>
       <c r="AT3" t="n">
-        <v>-508354000</v>
+        <v>-500146000</v>
       </c>
       <c r="AU3" t="n">
-        <v>694972000</v>
+        <v>712609000</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>198354000</v>
+        <v>224602000</v>
       </c>
       <c r="AX3" t="n">
-        <v>436951000</v>
+        <v>450371000</v>
       </c>
       <c r="AY3" t="n">
-        <v>258021000</v>
+        <v>262238000</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>120688000</v>
+        <v>133338000</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>6000000</v>
       </c>
       <c r="BC3" t="n">
-        <v>8057000</v>
+        <v>16445000</v>
       </c>
       <c r="BD3" t="n">
-        <v>-9320000</v>
+        <v>-13014000</v>
       </c>
       <c r="BE3" t="n">
-        <v>12726000</v>
+        <v>15339000</v>
       </c>
       <c r="BF3" t="n">
-        <v>510000</v>
+        <v>1378000</v>
       </c>
       <c r="BG3" t="n">
-        <v>4141000</v>
+        <v>12742000</v>
       </c>
       <c r="BH3" t="n">
-        <v>14872000</v>
+        <v>24137000</v>
       </c>
       <c r="BI3" t="n">
-        <v>12302000</v>
+        <v>18150000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-44000</v>
+        <v>-315000</v>
       </c>
       <c r="BK3" t="n">
-        <v>12346000</v>
+        <v>18465000</v>
       </c>
       <c r="BL3" t="n">
-        <v>85457000</v>
+        <v>68606000</v>
       </c>
       <c r="BM3" t="n">
-        <v>85457000</v>
+        <v>68606000</v>
       </c>
       <c r="BN3" t="n">
-        <v>9408000</v>
+        <v>26975000</v>
       </c>
       <c r="BO3" t="n">
-        <v>76049000</v>
+        <v>41631000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44773</v>
+        <v>45138</v>
       </c>
       <c r="B4" t="n">
         <v>2307513000</v>
@@ -2026,38 +2022,40 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>37413000</v>
+        <v>35108000</v>
       </c>
       <c r="F4" t="n">
-        <v>289816000</v>
+        <v>267566000</v>
       </c>
       <c r="G4" t="n">
-        <v>339368000</v>
+        <v>314410000</v>
       </c>
       <c r="H4" t="n">
-        <v>105086000</v>
+        <v>69203000</v>
       </c>
       <c r="I4" t="n">
-        <v>289816000</v>
+        <v>267566000</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>301955000</v>
+        <v>279302000</v>
       </c>
       <c r="L4" t="n">
-        <v>339368000</v>
+        <v>279302000</v>
       </c>
       <c r="M4" t="n">
-        <v>301955000</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
+        <v>279302000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
       <c r="O4" t="n">
-        <v>301955000</v>
+        <v>279302000</v>
       </c>
       <c r="P4" t="n">
-        <v>-178071000</v>
+        <v>-200373000</v>
       </c>
       <c r="Q4" t="n">
         <v>306364000</v>
@@ -2069,335 +2067,337 @@
         <v>105013000</v>
       </c>
       <c r="T4" t="n">
-        <v>66581000</v>
+        <v>52405000</v>
       </c>
       <c r="U4" t="n">
-        <v>38329000</v>
+        <v>920000</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>916000</v>
+        <v>920000</v>
       </c>
       <c r="Y4" t="n">
-        <v>37413000</v>
-      </c>
-      <c r="Z4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
       <c r="AA4" t="n">
-        <v>37413000</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>28252000</v>
+        <v>51485000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>35108000</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>35108000</v>
       </c>
       <c r="AF4" t="n">
-        <v>8702000</v>
+        <v>8048000</v>
       </c>
       <c r="AG4" t="n">
-        <v>733000</v>
+        <v>592000</v>
       </c>
       <c r="AH4" t="n">
-        <v>93000</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>7876000</v>
+        <v>7456000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>368536000</v>
+        <v>331707000</v>
       </c>
       <c r="AK4" t="n">
-        <v>235198000</v>
+        <v>211019000</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>3100000</v>
+        <v>2300000</v>
       </c>
       <c r="AN4" t="n">
-        <v>3100000</v>
+        <v>2300000</v>
       </c>
       <c r="AO4" t="n">
-        <v>7496000</v>
-      </c>
-      <c r="AP4" t="inlineStr"/>
+        <v>10365000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
       <c r="AQ4" t="n">
-        <v>12139000</v>
+        <v>11736000</v>
       </c>
       <c r="AR4" t="n">
-        <v>12139000</v>
+        <v>11736000</v>
       </c>
       <c r="AS4" t="n">
-        <v>212463000</v>
+        <v>186618000</v>
       </c>
       <c r="AT4" t="n">
-        <v>-500146000</v>
+        <v>-508354000</v>
       </c>
       <c r="AU4" t="n">
-        <v>712609000</v>
+        <v>694972000</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>224602000</v>
+        <v>198354000</v>
       </c>
       <c r="AX4" t="n">
-        <v>450371000</v>
+        <v>436951000</v>
       </c>
       <c r="AY4" t="n">
-        <v>262238000</v>
+        <v>258021000</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>133338000</v>
+        <v>120688000</v>
       </c>
       <c r="BB4" t="n">
-        <v>6000000</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>16445000</v>
+        <v>8057000</v>
       </c>
       <c r="BD4" t="n">
-        <v>-13014000</v>
+        <v>-9320000</v>
       </c>
       <c r="BE4" t="n">
-        <v>15339000</v>
+        <v>12726000</v>
       </c>
       <c r="BF4" t="n">
-        <v>1378000</v>
+        <v>510000</v>
       </c>
       <c r="BG4" t="n">
-        <v>12742000</v>
+        <v>4141000</v>
       </c>
       <c r="BH4" t="n">
-        <v>24137000</v>
+        <v>14872000</v>
       </c>
       <c r="BI4" t="n">
-        <v>18150000</v>
+        <v>12302000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-315000</v>
+        <v>-44000</v>
       </c>
       <c r="BK4" t="n">
-        <v>18465000</v>
+        <v>12346000</v>
       </c>
       <c r="BL4" t="n">
-        <v>68606000</v>
+        <v>85457000</v>
       </c>
       <c r="BM4" t="n">
-        <v>68606000</v>
+        <v>85457000</v>
       </c>
       <c r="BN4" t="n">
-        <v>26975000</v>
+        <v>9408000</v>
       </c>
       <c r="BO4" t="n">
-        <v>41631000</v>
+        <v>76049000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44408</v>
+        <v>45504</v>
       </c>
       <c r="B5" t="n">
-        <v>2307513000</v>
+        <v>2511084792</v>
       </c>
       <c r="C5" t="n">
-        <v>2307513000</v>
+        <v>2511084792</v>
       </c>
       <c r="D5" t="n">
-        <v>46434000</v>
+        <v>43550000</v>
       </c>
       <c r="E5" t="n">
-        <v>89845000</v>
+        <v>147813000</v>
       </c>
       <c r="F5" t="n">
-        <v>338260000</v>
+        <v>266034000</v>
       </c>
       <c r="G5" t="n">
-        <v>440432000</v>
+        <v>410572000</v>
       </c>
       <c r="H5" t="n">
-        <v>91933000</v>
+        <v>41678000</v>
       </c>
       <c r="I5" t="n">
-        <v>338260000</v>
+        <v>266034000</v>
       </c>
       <c r="J5" t="n">
-        <v>215000</v>
+        <v>19613000</v>
       </c>
       <c r="K5" t="n">
-        <v>350802000</v>
+        <v>282372000</v>
       </c>
       <c r="L5" t="n">
-        <v>386807000</v>
+        <v>308833000</v>
       </c>
       <c r="M5" t="n">
-        <v>350802000</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
+        <v>342752000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>60380000</v>
+      </c>
       <c r="O5" t="n">
-        <v>350802000</v>
+        <v>282372000</v>
       </c>
       <c r="P5" t="n">
-        <v>-60575000</v>
+        <v>-215773000</v>
       </c>
       <c r="Q5" t="n">
-        <v>306364000</v>
+        <v>310099000</v>
       </c>
       <c r="R5" t="n">
-        <v>105013000</v>
+        <v>114351000</v>
       </c>
       <c r="S5" t="n">
-        <v>105013000</v>
+        <v>114351000</v>
       </c>
       <c r="T5" t="n">
-        <v>141154000</v>
+        <v>250991000</v>
       </c>
       <c r="U5" t="n">
-        <v>38828000</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+        <v>48138000</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2802000</v>
+      </c>
+      <c r="W5" t="n">
+        <v>864000</v>
+      </c>
       <c r="X5" t="n">
-        <v>2823000</v>
+        <v>4881000</v>
       </c>
       <c r="Y5" t="n">
-        <v>36005000</v>
+        <v>39591000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>13130000</v>
       </c>
       <c r="AA5" t="n">
-        <v>36005000</v>
+        <v>26461000</v>
       </c>
       <c r="AB5" t="n">
-        <v>102326000</v>
+        <v>202853000</v>
       </c>
       <c r="AC5" t="n">
-        <v>53840000</v>
+        <v>108222000</v>
       </c>
       <c r="AD5" t="n">
-        <v>215000</v>
+        <v>6483000</v>
       </c>
       <c r="AE5" t="n">
-        <v>53625000</v>
+        <v>101739000</v>
       </c>
       <c r="AF5" t="n">
-        <v>23559000</v>
+        <v>61472000</v>
       </c>
       <c r="AG5" t="n">
-        <v>796000</v>
+        <v>3548000</v>
       </c>
       <c r="AH5" t="n">
-        <v>61000</v>
+        <v>556000</v>
       </c>
       <c r="AI5" t="n">
-        <v>22702000</v>
+        <v>57368000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>491956000</v>
+        <v>593743000</v>
       </c>
       <c r="AK5" t="n">
-        <v>297697000</v>
+        <v>349212000</v>
       </c>
       <c r="AL5" t="n">
-        <v>1027000</v>
+        <v>4486000</v>
       </c>
       <c r="AM5" t="n">
-        <v>3700000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>3700000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>5366000</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
-        <v>12542000</v>
+        <v>16338000</v>
       </c>
       <c r="AR5" t="n">
-        <v>12542000</v>
+        <v>16338000</v>
       </c>
       <c r="AS5" t="n">
-        <v>275062000</v>
+        <v>326045000</v>
       </c>
       <c r="AT5" t="n">
-        <v>-611636000</v>
+        <v>-652550000</v>
       </c>
       <c r="AU5" t="n">
-        <v>886698000</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
+        <v>978595000</v>
+      </c>
+      <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="n">
-        <v>287604000</v>
+        <v>947564000</v>
       </c>
       <c r="AX5" t="n">
-        <v>608294000</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>278404000</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
+        <v>31031000</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
-        <v>194259000</v>
+        <v>244531000</v>
       </c>
       <c r="BB5" t="n">
-        <v>48435000</v>
+        <v>13154000</v>
       </c>
       <c r="BC5" t="n">
-        <v>24435000</v>
+        <v>84971000</v>
       </c>
       <c r="BD5" t="n">
-        <v>-8361000</v>
+        <v>-9447000</v>
       </c>
       <c r="BE5" t="n">
-        <v>14208000</v>
+        <v>30754000</v>
       </c>
       <c r="BF5" t="n">
-        <v>1077000</v>
+        <v>10478000</v>
       </c>
       <c r="BG5" t="n">
-        <v>17511000</v>
+        <v>53186000</v>
       </c>
       <c r="BH5" t="n">
-        <v>38508000</v>
+        <v>6162000</v>
       </c>
       <c r="BI5" t="n">
-        <v>39685000</v>
+        <v>55594000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-325000</v>
+        <v>0</v>
       </c>
       <c r="BK5" t="n">
-        <v>40010000</v>
+        <v>55594000</v>
       </c>
       <c r="BL5" t="n">
-        <v>43196000</v>
+        <v>84650000</v>
       </c>
       <c r="BM5" t="n">
-        <v>43196000</v>
+        <v>84650000</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>170000</v>
       </c>
       <c r="BO5" t="n">
-        <v>43196000</v>
+        <v>84480000</v>
       </c>
     </row>
   </sheetData>
@@ -2603,411 +2603,411 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45504</v>
+        <v>44408</v>
       </c>
       <c r="B2" t="n">
-        <v>-15333000</v>
+        <v>7563000</v>
       </c>
       <c r="C2" t="n">
-        <v>-26192000</v>
+        <v>-123691000</v>
       </c>
       <c r="D2" t="n">
-        <v>14377000</v>
+        <v>59005000</v>
       </c>
       <c r="E2" t="n">
-        <v>-901000</v>
+        <v>-2802000</v>
       </c>
       <c r="F2" t="n">
-        <v>84650000</v>
+        <v>43196000</v>
       </c>
       <c r="G2" t="n">
-        <v>85457000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-467000</v>
-      </c>
+        <v>94187000</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>-340000</v>
+        <v>-50991000</v>
       </c>
       <c r="J2" t="n">
-        <v>-13695000</v>
+        <v>-63258000</v>
       </c>
       <c r="K2" t="n">
-        <v>-55000</v>
+        <v>12805000</v>
       </c>
       <c r="L2" t="n">
-        <v>-1825000</v>
+        <v>-5230000</v>
       </c>
       <c r="M2" t="n">
-        <v>-11815000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+        <v>-64686000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-45423000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-104428000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>59005000</v>
+      </c>
       <c r="Q2" t="n">
-        <v>-11815000</v>
+        <v>-19263000</v>
       </c>
       <c r="R2" t="n">
-        <v>-26192000</v>
+        <v>-19263000</v>
       </c>
       <c r="S2" t="n">
-        <v>14377000</v>
+        <v>59005000</v>
       </c>
       <c r="T2" t="n">
-        <v>27787000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-515000</v>
-      </c>
+        <v>1902000</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>1476000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>26767000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>26767000</v>
-      </c>
+        <v>518000</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
-        <v>59000</v>
+        <v>1384000</v>
       </c>
       <c r="Z2" t="n">
-        <v>960000</v>
+        <v>4186000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-901000</v>
+        <v>-2802000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-14432000</v>
+        <v>10365000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-3119000</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
+        <v>-362000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-17667000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-49076000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2885000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>28524000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>24691000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>24691000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>-2765000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>-919000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>-5191000</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45138</v>
+        <v>44773</v>
       </c>
       <c r="B3" t="n">
-        <v>13567000</v>
+        <v>37197000</v>
       </c>
       <c r="C3" t="n">
-        <v>-4477000</v>
+        <v>-53625000</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>-257000</v>
+      </c>
       <c r="F3" t="n">
-        <v>85457000</v>
+        <v>68606000</v>
       </c>
       <c r="G3" t="n">
-        <v>68606000</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
+        <v>43196000</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>16851000</v>
+        <v>25410000</v>
       </c>
       <c r="J3" t="n">
-        <v>-308000</v>
+        <v>-13623000</v>
       </c>
       <c r="K3" t="n">
-        <v>6000000</v>
+        <v>42435000</v>
       </c>
       <c r="L3" t="n">
-        <v>-1831000</v>
+        <v>-2211000</v>
       </c>
       <c r="M3" t="n">
-        <v>-4477000</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+        <v>-53625000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-21876000</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-21876000</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
       <c r="Q3" t="n">
-        <v>-4477000</v>
+        <v>-53625000</v>
       </c>
       <c r="R3" t="n">
-        <v>-4477000</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
+        <v>-53625000</v>
+      </c>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>3592000</v>
+        <v>1579000</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>921000</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
+        <v>1056000</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>2671000</v>
+        <v>523000</v>
       </c>
       <c r="Z3" t="n">
-        <v>2671000</v>
+        <v>780000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>-257000</v>
       </c>
       <c r="AB3" t="n">
-        <v>13567000</v>
+        <v>37454000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-116000</v>
+        <v>-786000</v>
       </c>
       <c r="AD3" t="n">
-        <v>14886000</v>
+        <v>32477000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-9611000</v>
+        <v>-13846000</v>
       </c>
       <c r="AF3" t="n">
-        <v>8787000</v>
+        <v>3248000</v>
       </c>
       <c r="AG3" t="n">
-        <v>15710000</v>
+        <v>43075000</v>
       </c>
       <c r="AH3" t="n">
-        <v>13458000</v>
+        <v>22781000</v>
       </c>
       <c r="AI3" t="n">
-        <v>13458000</v>
+        <v>22781000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-2001000</v>
-      </c>
-      <c r="AK3" t="inlineStr"/>
+        <v>4807000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
       <c r="AL3" t="n">
-        <v>-22292000</v>
+        <v>-48308000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44773</v>
+        <v>45138</v>
       </c>
       <c r="B4" t="n">
-        <v>37197000</v>
+        <v>13567000</v>
       </c>
       <c r="C4" t="n">
-        <v>-53625000</v>
+        <v>-4477000</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="E4" t="n">
-        <v>-257000</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
+        <v>85457000</v>
+      </c>
+      <c r="G4" t="n">
         <v>68606000</v>
       </c>
-      <c r="G4" t="n">
-        <v>43196000</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
       <c r="I4" t="n">
-        <v>25410000</v>
+        <v>16851000</v>
       </c>
       <c r="J4" t="n">
-        <v>-13623000</v>
+        <v>-308000</v>
       </c>
       <c r="K4" t="n">
-        <v>42435000</v>
+        <v>6000000</v>
       </c>
       <c r="L4" t="n">
-        <v>-2211000</v>
+        <v>-1831000</v>
       </c>
       <c r="M4" t="n">
-        <v>-53625000</v>
-      </c>
-      <c r="N4" t="n">
-        <v>-21876000</v>
-      </c>
-      <c r="O4" t="n">
-        <v>-21876000</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
+        <v>-4477000</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>-53625000</v>
+        <v>-4477000</v>
       </c>
       <c r="R4" t="n">
-        <v>-53625000</v>
-      </c>
-      <c r="S4" t="inlineStr"/>
+        <v>-4477000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
       <c r="T4" t="n">
-        <v>1579000</v>
+        <v>3592000</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>1056000</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
+        <v>921000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>523000</v>
+        <v>2671000</v>
       </c>
       <c r="Z4" t="n">
-        <v>780000</v>
+        <v>2671000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-257000</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>37454000</v>
+        <v>13567000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-786000</v>
+        <v>-116000</v>
       </c>
       <c r="AD4" t="n">
-        <v>32477000</v>
+        <v>14886000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-13846000</v>
+        <v>-9611000</v>
       </c>
       <c r="AF4" t="n">
-        <v>3248000</v>
+        <v>8787000</v>
       </c>
       <c r="AG4" t="n">
-        <v>43075000</v>
+        <v>15710000</v>
       </c>
       <c r="AH4" t="n">
-        <v>22781000</v>
+        <v>13458000</v>
       </c>
       <c r="AI4" t="n">
-        <v>22781000</v>
+        <v>13458000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>4807000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
+        <v>-2001000</v>
+      </c>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>-48308000</v>
+        <v>-22292000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44408</v>
+        <v>45504</v>
       </c>
       <c r="B5" t="n">
-        <v>7563000</v>
+        <v>-15333000</v>
       </c>
       <c r="C5" t="n">
-        <v>-123691000</v>
+        <v>-26192000</v>
       </c>
       <c r="D5" t="n">
-        <v>59005000</v>
+        <v>14377000</v>
       </c>
       <c r="E5" t="n">
-        <v>-2802000</v>
+        <v>-901000</v>
       </c>
       <c r="F5" t="n">
-        <v>43196000</v>
+        <v>84650000</v>
       </c>
       <c r="G5" t="n">
-        <v>94187000</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>85457000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-467000</v>
+      </c>
       <c r="I5" t="n">
-        <v>-50991000</v>
+        <v>-340000</v>
       </c>
       <c r="J5" t="n">
-        <v>-63258000</v>
+        <v>-13695000</v>
       </c>
       <c r="K5" t="n">
-        <v>12805000</v>
+        <v>-55000</v>
       </c>
       <c r="L5" t="n">
-        <v>-5230000</v>
+        <v>-1825000</v>
       </c>
       <c r="M5" t="n">
-        <v>-64686000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-45423000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-104428000</v>
-      </c>
-      <c r="P5" t="n">
-        <v>59005000</v>
-      </c>
+        <v>-11815000</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>-19263000</v>
+        <v>-11815000</v>
       </c>
       <c r="R5" t="n">
-        <v>-19263000</v>
+        <v>-26192000</v>
       </c>
       <c r="S5" t="n">
-        <v>59005000</v>
+        <v>14377000</v>
       </c>
       <c r="T5" t="n">
-        <v>1902000</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
+        <v>27787000</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-515000</v>
+      </c>
       <c r="V5" t="n">
-        <v>518000</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
+        <v>1476000</v>
+      </c>
+      <c r="W5" t="n">
+        <v>26767000</v>
+      </c>
+      <c r="X5" t="n">
+        <v>26767000</v>
+      </c>
       <c r="Y5" t="n">
-        <v>1384000</v>
+        <v>59000</v>
       </c>
       <c r="Z5" t="n">
-        <v>4186000</v>
+        <v>960000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-2802000</v>
+        <v>-901000</v>
       </c>
       <c r="AB5" t="n">
-        <v>10365000</v>
+        <v>-14432000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-362000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-17667000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-49076000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2885000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>28524000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>24691000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>24691000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>-2765000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>-919000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>-5191000</v>
-      </c>
+        <v>-3119000</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3536,187 +3536,187 @@
       </c>
       <c r="CY1" t="inlineStr">
         <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
       <c r="EJ1" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Kim Ling Beh', 'age': 67, 'title': 'Executive Chairman', 'yearBorn': 1958, 'fiscalYear': 2025, 'totalPay': 3628726, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Chern Wei Beh', 'age': 39, 'title': 'MD &amp; Executive Director', 'yearBorn': 1986, 'fiscalYear': 2025, 'totalPay': 1449923, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Hwee Sze  Beh', 'age': 40, 'title': 'Marketing &amp; Communications Manager and Executive Director', 'yearBorn': 1985, 'fiscalYear': 2025, 'totalPay': 180261, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Chin Siong Chong', 'age': 58, 'title': 'Corporate Finance Controller', 'yearBorn': 1967, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Thian Song Goh CPA, FCCA', 'age': 58, 'title': 'Financial Controller of VS Industry Vietnam Joint Stock Company', 'yearBorn': 1967, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Kim Sia  Beh', 'age': 61, 'title': 'Managing Director of VS Hanoi', 'yearBorn': 1964, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Ge  Zhang', 'age': 54, 'title': 'HR &amp; Adm. Director- V.S. Technology Ind. Park (Zhuhai) Co., Ltd. &amp; V.S. Ind. (Zhuhai) Co., Ltd.', 'yearBorn': 1971, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Ting On  Ng', 'age': 44, 'title': 'Company Secretary', 'yearBorn': 1981, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Kim Ling Beh', 'age': 67, 'title': 'Executive Chairman', 'yearBorn': 1958, 'fiscalYear': 2025, 'totalPay': 3628584, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Chern Wei Beh', 'age': 39, 'title': 'MD &amp; Executive Director', 'yearBorn': 1986, 'fiscalYear': 2025, 'totalPay': 1449866, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Hwee Sze  Beh', 'age': 40, 'title': 'Marketing &amp; Communications Manager and Executive Director', 'yearBorn': 1985, 'fiscalYear': 2025, 'totalPay': 180254, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Chin Siong Chong', 'age': 58, 'title': 'Corporate Finance Controller', 'yearBorn': 1967, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Thian Song Goh CPA, FCCA', 'age': 58, 'title': 'Financial Controller of VS Industry Vietnam Joint Stock Company', 'yearBorn': 1967, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Kim Sia  Beh', 'age': 61, 'title': 'Managing Director of VS Hanoi', 'yearBorn': 1964, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Ge  Zhang', 'age': 54, 'title': 'HR &amp; Adm. Director- V.S. Technology Ind. Park (Zhuhai) Co., Ltd. &amp; V.S. Ind. (Zhuhai) Co., Ltd.', 'yearBorn': 1971, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Ting On  Ng', 'age': 44, 'title': 'Company Secretary', 'yearBorn': 1981, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -3819,28 +3819,28 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.051</v>
       </c>
       <c r="V2" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.054</v>
       </c>
       <c r="W2" t="n">
-        <v>0.061</v>
+        <v>0.052</v>
       </c>
       <c r="X2" t="n">
-        <v>0.076</v>
+        <v>0.056</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.051</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.054</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.061</v>
+        <v>0.052</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.076</v>
+        <v>0.056</v>
       </c>
       <c r="AC2" t="n">
         <v>1197244800</v>
@@ -3852,28 +3852,28 @@
         <v>3.63</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.025</v>
+        <v>0.05</v>
       </c>
       <c r="AG2" t="n">
-        <v>664000</v>
+        <v>456000</v>
       </c>
       <c r="AH2" t="n">
-        <v>664000</v>
+        <v>456000</v>
       </c>
       <c r="AI2" t="n">
-        <v>187566</v>
+        <v>414474</v>
       </c>
       <c r="AJ2" t="n">
-        <v>434000</v>
+        <v>1315200</v>
       </c>
       <c r="AK2" t="n">
-        <v>434000</v>
+        <v>1315200</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.064</v>
+        <v>0.053</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.057</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
@@ -3882,16 +3882,16 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>160709440</v>
+        <v>140620752</v>
       </c>
       <c r="AQ2" t="n">
-        <v>175775935</v>
+        <v>128065324</v>
       </c>
       <c r="AR2" t="n">
         <v>0.048</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.076</v>
+        <v>0.097</v>
       </c>
       <c r="AT2" t="n">
         <v>0.760655</v>
@@ -3900,13 +3900,13 @@
         <v>0.039371</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.506972</v>
+        <v>2.1936004</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.05578</v>
+        <v>0.0588</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.05453</v>
+        <v>0.05523</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -3923,7 +3923,7 @@
         <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>170009376</v>
+        <v>149920704</v>
       </c>
       <c r="BD2" t="n">
         <v>0.00616</v>
@@ -3944,10 +3944,10 @@
         <v>2511084792</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.22728163</v>
+        <v>0.22727807</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.28158897</v>
+        <v>0.24639422</v>
       </c>
       <c r="BL2" t="n">
         <v>1767139200</v>
@@ -3965,16 +3965,16 @@
         <v>-0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>2.652</v>
+        <v>2.339</v>
       </c>
       <c r="BR2" t="n">
-        <v>20.029</v>
+        <v>17.663</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.32075477</v>
+        <v>-0.055555582</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BU2" t="n">
         <v>0.008947999999999999</v>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="BX2" t="n">
-        <v>0.064</v>
+        <v>0.056</v>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
@@ -4086,138 +4086,138 @@
       </c>
       <c r="CY2" t="inlineStr">
         <is>
+          <t>V.S. International Group Limited</t>
+        </is>
+      </c>
+      <c r="CZ2" t="n">
+        <v>9.803926000000001</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>V.S. INT'L</t>
+        </is>
+      </c>
+      <c r="DD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>1013131800000</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>0.0050000027</v>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>0.052 - 0.056</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="CZ2" t="n">
-        <v>1780385214</v>
-      </c>
-      <c r="DA2" t="inlineStr">
+      <c r="DI2" t="n">
+        <v>1782114437</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
         <is>
           <t>HKG</t>
         </is>
       </c>
-      <c r="DB2" t="inlineStr">
+      <c r="DK2" t="inlineStr">
         <is>
           <t>finmb_8087574</t>
         </is>
       </c>
-      <c r="DC2" t="inlineStr">
+      <c r="DL2" t="inlineStr">
         <is>
           <t>Asia/Hong_Kong</t>
         </is>
       </c>
-      <c r="DD2" t="inlineStr">
+      <c r="DM2" t="inlineStr">
         <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="DE2" t="n">
+      <c r="DN2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DF2" t="inlineStr">
+      <c r="DO2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="DG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>V.S. INT'L</t>
-        </is>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>V.S. International Group Limited</t>
-        </is>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DK2" t="n">
-        <v>0.008220002000000001</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>0.14736468</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>0.009470005</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>0.17366596</v>
-      </c>
-      <c r="DO2" t="n">
+      <c r="DP2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ2" t="n">
         <v>15</v>
       </c>
-      <c r="DP2" t="n">
+      <c r="DR2" t="n">
         <v>15</v>
       </c>
-      <c r="DQ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>-8.571424499999999</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="DT2" t="b">
-        <v>0</v>
+      <c r="DS2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
       </c>
       <c r="DU2" t="n">
-        <v>1013131800000</v>
+        <v>414474</v>
       </c>
       <c r="DV2" t="n">
-        <v>-0.0059999973</v>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>0.061 - 0.076</t>
-        </is>
+        <v>0.008000001</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>0.16666669</v>
       </c>
       <c r="DX2" t="inlineStr">
         <is>
-          <t>HKSE</t>
+          <t>0.048 - 0.097</t>
         </is>
       </c>
       <c r="DY2" t="n">
-        <v>187566</v>
+        <v>-0.041</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.016000003</v>
+        <v>-0.4226804</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.33333337</v>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>0.048 - 0.076</t>
-        </is>
+        <v>-5.555558</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>1727175540</v>
       </c>
       <c r="EC2" t="n">
-        <v>-0.0119999945</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>-0.15789467</v>
+        <v>1727175540</v>
+      </c>
+      <c r="ED2" t="b">
+        <v>0</v>
       </c>
       <c r="EE2" t="n">
-        <v>32.075478</v>
+        <v>-0</v>
       </c>
       <c r="EF2" t="n">
-        <v>1727175540</v>
+        <v>-0.002799999</v>
       </c>
       <c r="EG2" t="n">
-        <v>1727175540</v>
-      </c>
-      <c r="EH2" t="b">
-        <v>0</v>
+        <v>-0.04761903</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>0.0007700026</v>
       </c>
       <c r="EI2" t="n">
-        <v>-0</v>
+        <v>0.013941745</v>
       </c>
       <c r="EJ2" t="inlineStr"/>
     </row>
